--- a/excel_templates/DCF_Model_Template_MA_Buy.xlsx
+++ b/excel_templates/DCF_Model_Template_MA_Buy.xlsx
@@ -16,6 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值对比" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敏感性分析" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键假设清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业绩承诺可行性分析" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配套募资概览" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="募投项目独立DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="含募投合并调整" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +62,30 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +116,14 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -105,11 +137,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,6 +228,17 @@
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,6 +613,15 @@
           <t>某并购方企业 — M&amp;A 并购置入交易概览</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -678,6 +758,1567 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>业绩承诺可行性分析（条件启用：重组报告书含业绩承诺条款时）</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>一、业绩承诺核心条款</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>条款</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr"/>
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="E4" s="24" t="inlineStr"/>
+      <c r="F4" s="24" t="inlineStr"/>
+      <c r="G4" s="24" t="inlineStr"/>
+      <c r="H4" s="24" t="inlineStr"/>
+      <c r="I4" s="24" t="inlineStr"/>
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>承诺方及持股比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>承诺期</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>各年承诺净利润</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>触发补偿条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>补偿方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>补偿上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>股份解锁安排</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>募投排除条款（如有）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>二、历史实际 vs 业绩承诺 vs DCF预测 核心数据对比（T=基准年）</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>T-1实际</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>T实际</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>T+1E承诺</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>T+2E(隐含)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>T+3E(隐含)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr"/>
+      <c r="H16" s="24" t="inlineStr"/>
+      <c r="I16" s="24" t="inlineStr"/>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>营业收入（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>净利润（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>净利率</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>净利润增速 vs 上年</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>DCF隐含净利（估算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>承诺 vs DCF隐含差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>三、增长驱动力拆解</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>驱动因素</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>T-1→T 实际</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>T→T+1E</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>T+1E→T+2E</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>T+2E→T+3E</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr"/>
+      <c r="G26" s="24" t="inlineStr"/>
+      <c r="H26" s="24" t="inlineStr"/>
+      <c r="I26" s="24" t="inlineStr"/>
+      <c r="J26" s="24" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>净利润变化额</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>净利润增速</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>收入增速</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>净利率变动</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>期间费用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>增长主因</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>四、压力测试矩阵（收入增速情景 × 承诺年份）</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>收入增速情景</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>{T+1}净利(万)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>{T+2}净利(万)</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>{T+3}净利(万)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>N年累计</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>触发补偿?</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>缺口%</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr"/>
+      <c r="I36" s="24" t="inlineStr"/>
+      <c r="J36" s="24" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>DCF基准（按预测增速）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>收入 +5%/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>收入 +3%/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>收入 +0%/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>五、综合判断（七维度）</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+      <c r="I43" s="23" t="n"/>
+      <c r="J43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>判断维度</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>评级</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>关键计算/说明</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr"/>
+      <c r="E44" s="24" t="inlineStr"/>
+      <c r="F44" s="24" t="inlineStr"/>
+      <c r="G44" s="24" t="inlineStr"/>
+      <c r="H44" s="24" t="inlineStr"/>
+      <c r="I44" s="24" t="inlineStr"/>
+      <c r="J44" s="24" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>承诺设定水平（合理/偏乐观/偏保守）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>隐含增长率（vs 历史趋势）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>核心依赖项（收入增长 / 利润率改善）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>单点风险（收入增速每少1pct→净利缺口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>触发补偿概率（低/中/高）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>补偿保护力度（承诺方持股% + 补偿上限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>商誉联动风险（商誉/净资产比%）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A25:J25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>配套募集资金概览与双重摊薄分析（条件启用：重组报告书含配套募资方案时）</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>一、配套募资方案</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>金额/数值</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="E4" s="24" t="inlineStr"/>
+      <c r="F4" s="24" t="inlineStr"/>
+      <c r="G4" s="24" t="inlineStr"/>
+      <c r="H4" s="24" t="inlineStr"/>
+      <c r="I4" s="24" t="inlineStr"/>
+      <c r="J4" s="24" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>募资总额（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>发行方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>发行对象范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>锁定期</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>用途1: 支付现金对价（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>用途2: 交易税费及中介费（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>用途3: 补充上市公司流动资金（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>用途4: 标的公司募投项目建设（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>二、双重摊薄对比</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>仅发股购买</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>发股+配套募资</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr"/>
+      <c r="F18" s="24" t="inlineStr"/>
+      <c r="G18" s="24" t="inlineStr"/>
+      <c r="H18" s="24" t="inlineStr"/>
+      <c r="I18" s="24" t="inlineStr"/>
+      <c r="J18" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>发行前总股本</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>发股购买新增股数</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>配套募资新增股数（估算）</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>发行后总股本</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>稀释率</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="25" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>归母净资产</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>每股BPS</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>每股价值变化</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>万股</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A10:J10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>标的公司募投项目独立DCF分析（条件启用：配套资金含标的项目建设用途）</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>一、项目概况</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>实施主体</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>总投资（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>建设期（年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>募资投入金额（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>自有资金缺口（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>二、分年投资计划（万元）</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Y1(建设)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Y2(建设)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Y3(投产)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>建筑工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>设备购置</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>软件</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>预备费</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>CAPEX合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>三、增量收入预测（万元）</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>Y10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>达产率</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>增量营业收入</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>增量营业成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>增量毛利</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>四、项目独立FCFF与估值</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>Y10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>增量毛利</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>减: 增量期间费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>减: 所得税</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25">
+        <f> 增量NOPAT</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>加: D&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>减: CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>减: ΔNWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26">
+        <f> 项目FCFF</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>估值结果</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="23" t="n"/>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>折现率（WACC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>项目NPV（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>项目IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>静态投资回收期（年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>动态投资回收期（年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>deal报告披露IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>偏差分析</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A29:J29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>含募投备考合并调整（条件启用：募投项目独立DCF已生成时）</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>一、原标的FCFF（评估报告） vs 含募投合并FCFF</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="23" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>T+1E</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>T+2E</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>T+3E</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>T+4E</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>T+5E</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>永续期</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr"/>
+      <c r="I4" s="24" t="inlineStr"/>
+      <c r="J4" s="24" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>原标的FCFF（评估报告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>+ 募投项目增量FCFF（来自募投DCF Sheet）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26">
+        <f> 含募投标的合并FCFF</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>折现率（WACC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>折现系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>含募投FCFF现值</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>终值</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>含募投标的企业整体价值(EV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>减: 付息债务（考虑募资注入后）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>含募投标的股权价值</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>二、原评估值 vs 含募投价值 对比判断</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>金额（万元）</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr"/>
+      <c r="E20" s="24" t="inlineStr"/>
+      <c r="F20" s="24" t="inlineStr"/>
+      <c r="G20" s="24" t="inlineStr"/>
+      <c r="H20" s="24" t="inlineStr"/>
+      <c r="I20" s="24" t="inlineStr"/>
+      <c r="J20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>原评估值（交易定价基础）</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>不能动——评估报告基准日结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>含募投标的股权价值</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>含配套资金注入后增量</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>差额 = 净新增价值</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>正=募投创造价值 / 负=质疑募资必要性</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>⚠ 关键判断：差额是否为正？ → 正=募投成立 / 负=质疑募资必要性 / 差额度 = 净新增(损失)价值</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>备注：原评估报告是交易定价基础，不能直接修改。本表仅作为含募投情景的备考参考，不构成对评估报告的质疑。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -698,6 +2339,15 @@
           <t>某并购方企业 — 历史财务数据</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -705,6 +2355,15 @@
           <t>一、合并利润表（万元）</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -798,6 +2457,15 @@
           <t>二、关键财务指标</t>
         </is>
       </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -859,6 +2527,15 @@
           <t>三、资产负债表关键项目（万元，基准日）</t>
         </is>
       </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1010,6 +2687,15 @@
           <t>四、折旧摊销（万元，基准年）</t>
         </is>
       </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1067,6 +2753,15 @@
           <t>五、CAPEX（万元，基准年）</t>
         </is>
       </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1106,6 +2801,15 @@
           <t>某并购方企业 — 可比公司分析与WACC计算</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1113,6 +2817,15 @@
           <t>一、可比公司 βU 去杠杆矩阵</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1282,6 +2995,15 @@
           <t>二、WACC 计算参数</t>
         </is>
       </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1512,6 +3234,15 @@
           <t>某并购方企业 — 独立DCF (独立口径)</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1519,6 +3250,15 @@
           <t>一、收入预测</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1613,6 +3353,15 @@
           <t>二、利润预测</t>
         </is>
       </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1707,6 +3456,15 @@
           <t>三、FCFF 计算</t>
         </is>
       </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1875,6 +3633,15 @@
           <t>四、DCF 折现（WACC=8.80%）</t>
         </is>
       </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1969,6 +3736,15 @@
           <t>五、估值结果</t>
         </is>
       </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2129,6 +3905,15 @@
           <t>某并购方企业 — 标的公司FCFF 预测</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2136,6 +3921,15 @@
           <t>标的公司: 某矿业标的</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2331,10 +4125,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>-13500</v>
@@ -2343,10 +4137,10 @@
         <v>-4500</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2398,6 +4192,15 @@
           <t>某并购方企业 — 备考合并DCF (合并口径)</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2405,6 +4208,15 @@
           <t>一、收入预测</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2499,6 +4311,15 @@
           <t>二、利润预测</t>
         </is>
       </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2593,6 +4414,15 @@
           <t>三、FCFF 计算</t>
         </is>
       </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2761,6 +4591,15 @@
           <t>四、DCF 折现（WACC=9.10%）</t>
         </is>
       </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2855,6 +4694,15 @@
           <t>五、估值结果</t>
         </is>
       </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3015,6 +4863,15 @@
           <t>某并购方企业 — 估值对比分析</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -3022,6 +4879,15 @@
           <t>独立估值 vs 合并估值 每股对比</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3125,6 +4991,15 @@
           <t>某并购方企业 — 敏感性分析</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -3132,6 +5007,15 @@
           <t>WACC × g 敏感性矩阵 (每股价值, 元)</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr"/>
@@ -3321,6 +5205,15 @@
           <t>图例: 绿底红字=基准情景 | 绿色=高于基准 | 红色=低于基准</t>
         </is>
       </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3328,6 +5221,15 @@
           <t>基准: WACC=9.10%, g=2.0% → 每股 9.27元</t>
         </is>
       </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3335,6 +5237,15 @@
           <t>敏感性提示</t>
         </is>
       </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3384,6 +5295,15 @@
           <t>某并购方企业 — 关键假设清单</t>
         </is>
       </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -3391,6 +5311,15 @@
           <t>建模完成后强制输出（SKILL.md §13.1）</t>
         </is>
       </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3684,6 +5613,15 @@
           <t>敏感性提示 (SKILL.md §13.2)</t>
         </is>
       </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3719,6 +5657,15 @@
           <t>待验证/风险提示 (SKILL.md §13.3)</t>
         </is>
       </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3750,10 +5697,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
